--- a/SLR/Full-Paper-Read/Paper-Review/PS09.xlsx
+++ b/SLR/Full-Paper-Read/Paper-Review/PS09.xlsx
@@ -11,8 +11,24 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment authorId="0" ref="I2">
+      <text>
+        <t xml:space="preserve">PS14 presents a systematic mapping study on automated analysis of feature models (AAFM).
+	-Adnan Ashraf</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="57">
   <si>
     <t>ID</t>
   </si>
@@ -26,94 +42,112 @@
     <t>The paper proposes the following contributions:</t>
   </si>
   <si>
-    <t>The paper discusses the ecosystem of software that could run on CPS if we open them up for third party developers. In this ecosystem, we need a Trusted Execution Environment and a secure world for some applications. They suggest a second OS next to Android, and running securely applications in this environment. They discuss challenges and evaluate. They discuss threat models. The paper also has a link to the source code to the project. They do not discuss how industry and academia can collaborate.</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <i/>
+        <color theme="1"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t xml:space="preserve">The paper focuses on Automated Analysis of Feature Models (AAFM) and provides an overview of the evolution of this field since 2010 by performing a systematic mapping study. Among the emerged research opportunities: 
+- An emerging challenge in this area is the configuration of a diversity of distributed Software Product Line (SPL) descriptions, sometimes known as software </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <i/>
+        <color theme="1"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>ecosystems</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <i/>
+        <color theme="1"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t xml:space="preserve">. As SPLs grow, configuring and maintaining them become an unfeasible task for a small group. Also, different stakeholders and privacy policies encourage the use of visibility restrictions for the configurable parts. We think that there is still work to be done in this area like, for example, to enable the parallel configuration of those open and distributed SPLs.
+- The number of different scenarios where AAFM can be applied have been proved to be very large and we envision that there will be more and more scenarios where it will be applied in the future. </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <i/>
+        <color theme="1"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>Ecosystems</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <i/>
+        <color theme="1"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t>, cyber-physical systems, robotics, big data or the internet of the things are only some examples where variability is a first-class citizen and can use AAFM techniques in their development.</t>
+    </r>
+  </si>
+  <si>
+    <t>This paper is partially out of scope but, among the research opportunities identified,  the authors mention ecosystems and the variability as challenge</t>
+  </si>
+  <si>
+    <t>CPS Case Study / Example availability</t>
   </si>
   <si>
     <t>&lt;add your comment here if any&gt;</t>
   </si>
   <si>
-    <t>CPS Case Study / Example availability</t>
-  </si>
-  <si>
-    <t>Yes, they have an example. A proof-of-concept of an application running in the Trusted Execution Environment.</t>
-  </si>
-  <si>
     <t>SECO Tools Availability (add repository or website in the comment)</t>
   </si>
   <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Related Challenge - See SPE paper (Write Others in comment cell)</t>
+  </si>
+  <si>
+    <t>Modeling and Model-Driven Engineering</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>n.a.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feature models, variability </t>
+  </si>
+  <si>
+    <t>Does it contribute to answer RQ1?</t>
+  </si>
+  <si>
     <t>Y</t>
   </si>
   <si>
-    <t>https://bitbucket.org/vincent_raes/</t>
-  </si>
-  <si>
-    <t>Related Challenge - See SPE paper (Write Others in comment cell)</t>
-  </si>
-  <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>n.a.</t>
-  </si>
-  <si>
-    <t>Primarilly: cybersecutiry, but also data (trusting data - veracity)</t>
-  </si>
-  <si>
-    <t>Does it contribute to answer RQ1?</t>
-  </si>
-  <si>
-    <t>If CPS hardware is "opened" for third party developers - how could we ensure it's secure.</t>
-  </si>
-  <si>
     <t>Does the paper present methods, tools, and benefits in terms of industry/academia collaboration? If so, write what methods, tools, and benefits in the comment column</t>
   </si>
   <si>
-    <t>They identify a problem, implement a solution, and compare with other similar solutions.</t>
-  </si>
-  <si>
     <t>Does it contribute to answer RQ2?</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>They do not discuss industry-academia relations as far as I can tell.</t>
-  </si>
-  <si>
     <t>Application Domain(s) (at least one or domain independent)</t>
   </si>
   <si>
     <t>Application Domain Independent</t>
   </si>
   <si>
-    <t>Applicable for many domains. The paper mentions four examples: proprietary local data proecssing (IIoT), Leasing machines (shared computers), Onboard Computers (Automotive, Marine, ...), and home care (health sector).</t>
-  </si>
-  <si>
     <t>Quality Evaluation (From 1 to 10) - From "Quality" Tab</t>
   </si>
   <si>
-    <t>They wrote some requirements and evaluate based on them. It seems to people were involved.</t>
-  </si>
-  <si>
-    <t>What if third party people were let into CPS - they could use hardware for additional services --&gt; Open source eco system where a CPS us used more.</t>
-  </si>
-  <si>
-    <t>Challenge: data and sofware in by CPS developed by third party.</t>
-  </si>
-  <si>
-    <t>Sometimes: solution is access control, but they suggest running the sofware in a secure environment.</t>
-  </si>
-  <si>
-    <t>They propose TrustZone (a TEE - Trusted Execution Environment), to run secure serice in CPS. They evaluate the solution based on performance, security and ease of use.</t>
-  </si>
-  <si>
-    <t>RQ1 In the SECO, what are the main challenges faced during the CPS development?</t>
-  </si>
-  <si>
-    <t>RQ2 How do industry and academia collaborate and benefit in the SECO for CPS development?</t>
+    <t>RQ1: In the SECO, what are the main challenges faced during the CPS development?</t>
+  </si>
+  <si>
+    <t>RQ2: How do industry and academia collaborate and benefit in the SECO for CPS development?</t>
   </si>
   <si>
     <t>Assessment Criterion (Question)</t>
@@ -156,9 +190,6 @@
   </si>
   <si>
     <t>Was there a control group with which to compare treatments?</t>
-  </si>
-  <si>
-    <t>(They compare with another similar solution from Huawei)</t>
   </si>
   <si>
     <t>Are the data collection methods adequately described (defined)?</t>
@@ -222,7 +253,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -249,25 +280,18 @@
     </font>
     <font/>
     <font>
-      <i/>
-      <u/>
-      <sz val="10.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
+      <sz val="12.0"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Lato"/>
     </font>
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="11">
@@ -593,7 +617,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="57">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -612,7 +636,7 @@
     <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="9" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -626,13 +650,13 @@
     </xf>
     <xf borderId="16" fillId="4" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="15" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="17" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="18" fillId="5" fontId="5" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment horizontal="right"/>
+    </xf>
+    <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="16" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
@@ -644,15 +668,18 @@
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
     <xf borderId="20" fillId="4" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="16" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="19" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf borderId="19" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
     <xf borderId="21" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
@@ -662,16 +689,13 @@
     <xf borderId="18" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="22" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="23" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="22" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="23" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -680,19 +704,19 @@
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="7" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="24" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf borderId="25" fillId="7" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="7" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="24" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -700,37 +724,34 @@
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="8" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="24" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf borderId="25" fillId="8" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="8" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="24" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="24" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf borderId="25" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="10" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="24" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf borderId="25" fillId="10" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="10" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
@@ -1050,7 +1071,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="17">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
@@ -1077,7 +1098,7 @@
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
       <c r="I5" s="21" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -1085,28 +1106,28 @@
         <v>4.0</v>
       </c>
       <c r="B6" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="D6" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="E6" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="F6" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="23" t="s">
         <v>14</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="23" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -1114,28 +1135,28 @@
         <v>5.0</v>
       </c>
       <c r="B7" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="24" t="s">
         <v>16</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>9</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
       <c r="G7" s="25"/>
       <c r="H7" s="18"/>
-      <c r="I7" s="23" t="s">
-        <v>17</v>
+      <c r="I7" s="26" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="16">
         <v>6.0</v>
       </c>
-      <c r="B8" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="24" t="s">
+      <c r="B8" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="28" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="25"/>
@@ -1143,8 +1164,8 @@
       <c r="F8" s="25"/>
       <c r="G8" s="25"/>
       <c r="H8" s="18"/>
-      <c r="I8" s="23" t="s">
-        <v>19</v>
+      <c r="I8" s="26" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -1152,18 +1173,18 @@
         <v>7.0</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>21</v>
+        <v>18</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>9</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="25"/>
       <c r="F9" s="25"/>
       <c r="G9" s="25"/>
       <c r="H9" s="18"/>
-      <c r="I9" s="28" t="s">
-        <v>22</v>
+      <c r="I9" s="21" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -1171,28 +1192,28 @@
         <v>8.0</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="23" t="s">
-        <v>25</v>
+        <v>19</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="26" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -1200,53 +1221,37 @@
         <v>9.0</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="31">
+        <v>21</v>
+      </c>
+      <c r="C11" s="32">
         <f>Quality!C29</f>
-        <v>5.925925926</v>
+        <v>10</v>
       </c>
       <c r="D11" s="25"/>
       <c r="E11" s="25"/>
       <c r="F11" s="25"/>
       <c r="G11" s="25"/>
       <c r="H11" s="25"/>
-      <c r="I11" s="28" t="s">
-        <v>27</v>
+      <c r="I11" s="21" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="B14" s="32" t="s">
-        <v>28</v>
+      <c r="B14" s="33" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="B15" s="32" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="B16" s="32" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="B17" s="32" t="s">
-        <v>31</v>
-      </c>
-    </row>
+      <c r="B15" s="33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1"/>
+    <row r="17" ht="15.75" customHeight="1"/>
     <row r="18" ht="15.75" customHeight="1"/>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="B19" s="33" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="B20" s="33" t="s">
-        <v>33</v>
-      </c>
-    </row>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -2276,13 +2281,11 @@
       <formula1>"n.a.,Y,N"</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink r:id="rId1" ref="I5"/>
-  </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
   <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -2303,10 +2306,10 @@
     <row r="1">
       <c r="A1" s="34"/>
       <c r="B1" s="35" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D1" s="36"/>
       <c r="E1" s="37"/>
@@ -2314,10 +2317,10 @@
     </row>
     <row r="2">
       <c r="A2" s="39" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C2" s="41">
         <v>1.0</v>
@@ -2329,7 +2332,7 @@
     <row r="3">
       <c r="A3" s="43"/>
       <c r="B3" s="40" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C3" s="41">
         <v>1.0</v>
@@ -2341,7 +2344,7 @@
     <row r="4">
       <c r="A4" s="43"/>
       <c r="B4" s="40" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C4" s="41">
         <v>1.0</v>
@@ -2352,7 +2355,7 @@
     <row r="5">
       <c r="A5" s="43"/>
       <c r="B5" s="40" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C5" s="41">
         <v>1.0</v>
@@ -2363,7 +2366,7 @@
     <row r="6">
       <c r="A6" s="43"/>
       <c r="B6" s="40" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C6" s="41">
         <v>1.0</v>
@@ -2374,7 +2377,7 @@
     <row r="7">
       <c r="A7" s="44"/>
       <c r="B7" s="40" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C7" s="41">
         <v>1.0</v>
@@ -2390,13 +2393,13 @@
     </row>
     <row r="8">
       <c r="A8" s="46" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C8" s="48">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="D8" s="36"/>
       <c r="E8" s="36"/>
@@ -2404,10 +2407,10 @@
     <row r="9">
       <c r="A9" s="43"/>
       <c r="B9" s="47" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C9" s="48">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="D9" s="36"/>
       <c r="E9" s="36"/>
@@ -2415,10 +2418,10 @@
     <row r="10">
       <c r="A10" s="43"/>
       <c r="B10" s="47" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C10" s="48">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="D10" s="36"/>
       <c r="E10" s="36"/>
@@ -2426,24 +2429,21 @@
     <row r="11">
       <c r="A11" s="43"/>
       <c r="B11" s="47" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C11" s="48">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="D11" s="36"/>
       <c r="E11" s="36"/>
-      <c r="F11" s="32" t="s">
-        <v>48</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="43"/>
       <c r="B12" s="47" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C12" s="48">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D12" s="36"/>
       <c r="E12" s="36"/>
@@ -2451,10 +2451,10 @@
     <row r="13">
       <c r="A13" s="43"/>
       <c r="B13" s="47" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C13" s="48">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D13" s="36"/>
       <c r="E13" s="36"/>
@@ -2462,10 +2462,10 @@
     <row r="14">
       <c r="A14" s="43"/>
       <c r="B14" s="47" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C14" s="48">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D14" s="36"/>
       <c r="E14" s="36"/>
@@ -2473,10 +2473,10 @@
     <row r="15">
       <c r="A15" s="43"/>
       <c r="B15" s="47" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C15" s="48">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D15" s="36"/>
       <c r="E15" s="36"/>
@@ -2484,10 +2484,10 @@
     <row r="16">
       <c r="A16" s="43"/>
       <c r="B16" s="47" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C16" s="48">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D16" s="36"/>
       <c r="E16" s="36"/>
@@ -2495,10 +2495,10 @@
     <row r="17">
       <c r="A17" s="43"/>
       <c r="B17" s="47" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C17" s="48">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="D17" s="36"/>
       <c r="E17" s="36"/>
@@ -2506,7 +2506,7 @@
     <row r="18">
       <c r="A18" s="43"/>
       <c r="B18" s="47" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C18" s="48">
         <v>1.0</v>
@@ -2517,10 +2517,10 @@
     <row r="19">
       <c r="A19" s="44"/>
       <c r="B19" s="47" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="C19" s="48">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="D19" s="45">
         <f>COUNTIF(B8:B19,"&lt;&gt;text")</f>
@@ -2528,18 +2528,18 @@
       </c>
       <c r="E19" s="45">
         <f>(SUM(C8:C19)/D19)*10</f>
-        <v>3.333333333</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="49" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B20" s="50" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C20" s="51">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="D20" s="36"/>
       <c r="E20" s="36"/>
@@ -2547,10 +2547,10 @@
     <row r="21">
       <c r="A21" s="43"/>
       <c r="B21" s="50" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C21" s="51">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D21" s="36"/>
       <c r="E21" s="36"/>
@@ -2558,10 +2558,10 @@
     <row r="22">
       <c r="A22" s="43"/>
       <c r="B22" s="50" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C22" s="51">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D22" s="36"/>
       <c r="E22" s="36"/>
@@ -2569,9 +2569,9 @@
     <row r="23">
       <c r="A23" s="43"/>
       <c r="B23" s="50" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" s="52">
+        <v>50</v>
+      </c>
+      <c r="C23" s="51">
         <v>1.0</v>
       </c>
       <c r="D23" s="37"/>
@@ -2581,10 +2581,10 @@
     <row r="24">
       <c r="A24" s="43"/>
       <c r="B24" s="50" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C24" s="51">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="D24" s="37"/>
       <c r="E24" s="37"/>
@@ -2593,29 +2593,29 @@
     <row r="25">
       <c r="A25" s="44"/>
       <c r="B25" s="50" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25" s="52">
-        <v>1.0</v>
-      </c>
-      <c r="D25" s="53">
+        <v>52</v>
+      </c>
+      <c r="C25" s="51">
+        <v>1.0</v>
+      </c>
+      <c r="D25" s="52">
         <f>COUNTIF(B20:B25,"&lt;&gt;text")</f>
         <v>6</v>
       </c>
-      <c r="E25" s="53">
+      <c r="E25" s="52">
         <f>(SUM(C20:C25)/D25)*10</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F25" s="42"/>
     </row>
     <row r="26">
-      <c r="A26" s="54" t="s">
-        <v>64</v>
-      </c>
-      <c r="B26" s="55" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" s="56">
+      <c r="A26" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="54" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="55">
         <v>1.0</v>
       </c>
       <c r="D26" s="37"/>
@@ -2624,10 +2624,10 @@
     </row>
     <row r="27">
       <c r="A27" s="43"/>
-      <c r="B27" s="55" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" s="56">
+      <c r="B27" s="54" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="55">
         <v>1.0</v>
       </c>
       <c r="D27" s="37"/>
@@ -2636,30 +2636,30 @@
     </row>
     <row r="28">
       <c r="A28" s="44"/>
-      <c r="B28" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="C28" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="D28" s="53">
+      <c r="B28" s="54" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="55">
+        <v>1.0</v>
+      </c>
+      <c r="D28" s="52">
         <f>COUNTIF(B26:B28,"&lt;&gt;text")</f>
         <v>3</v>
       </c>
-      <c r="E28" s="53">
+      <c r="E28" s="52">
         <f>(SUM(C26:C28)/D28)*10</f>
         <v>10</v>
       </c>
       <c r="F28" s="42"/>
     </row>
     <row r="29">
-      <c r="B29" s="57">
+      <c r="B29" s="56">
         <f>COUNTIF(B2:B28,"&lt;&gt;text")</f>
         <v>27</v>
       </c>
-      <c r="C29" s="57">
+      <c r="C29" s="56">
         <f>(SUM(C2:C28)/B29)*10</f>
-        <v>5.925925926</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
